--- a/LubanConfig/Config/Datas/#hero.xlsx
+++ b/LubanConfig/Config/Datas/#hero.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -45,9 +45,6 @@
     <t>##group</t>
   </si>
   <si>
-    <t>c,s</t>
-  </si>
-  <si>
     <t>c</t>
   </si>
   <si>
@@ -60,24 +57,63 @@
     <t>描述</t>
   </si>
   <si>
-    <t>描述1</t>
-  </si>
-  <si>
-    <t>描述2</t>
-  </si>
-  <si>
-    <t>描述3</t>
-  </si>
-  <si>
-    <t>英雄1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄3</t>
+    <t>英雄1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Hero/1001/Hero1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄1001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -121,8 +157,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -403,93 +442,138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="13.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
+        <v>100</v>
+      </c>
+      <c r="G5" s="1">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
+      <c r="H5" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
